--- a/data/trans_camb/P16A15-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 13,19</t>
+          <t>6,25; 12,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,31; 12,97</t>
+          <t>5,94; 12,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 16,22</t>
+          <t>8,79; 16,41</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>6,15; 12,23</t>
+          <t>5,86; 12,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 12,62</t>
+          <t>5,78; 12,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,87; 18,6</t>
+          <t>12,02; 18,24</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,21; 11,72</t>
+          <t>7,17; 11,67</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,84</t>
+          <t>6,93; 11,81</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,75; 16,62</t>
+          <t>11,82; 16,78</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>50,93; 128,79</t>
+          <t>49,8; 131,31</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>51,01; 128,0</t>
+          <t>46,21; 128,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>69,79; 158,1</t>
+          <t>70,18; 164,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>36,82; 88,4</t>
+          <t>33,85; 85,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,11; 90,88</t>
+          <t>34,49; 90,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>69,16; 132,86</t>
+          <t>70,64; 130,81</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,34; 92,55</t>
+          <t>48,29; 91,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>44,69; 93,36</t>
+          <t>47,58; 92,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,47; 131,78</t>
+          <t>80,42; 132,92</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,46; 4,24</t>
+          <t>1,23; 4,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,57</t>
+          <t>1,85; 4,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,02; 7,94</t>
+          <t>3,37; 7,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,41</t>
+          <t>0,43; 3,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 4,53</t>
+          <t>1,75; 4,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,33; 37,64</t>
+          <t>5,29; 37,28</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,32</t>
+          <t>1,45; 3,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,15</t>
+          <t>2,22; 4,22</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 23,86</t>
+          <t>5,53; 22,6</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>36,15; 162,03</t>
+          <t>30,26; 153,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>49,84; 184,24</t>
+          <t>45,67; 173,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>96,76; 310,43</t>
+          <t>88,47; 296,89</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>12,38; 134,16</t>
+          <t>9,67; 128,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>38,58; 170,27</t>
+          <t>41,98; 175,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>153,23; 1347,14</t>
+          <t>151,12; 1314,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>33,92; 116,33</t>
+          <t>38,07; 120,8</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>55,28; 147,13</t>
+          <t>58,12; 148,78</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>170,0; 781,09</t>
+          <t>167,41; 747,18</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 6,13</t>
+          <t>-0,14; 6,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 3,75</t>
+          <t>-1,15; 3,83</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,84</t>
+          <t>2,86; 8,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,86</t>
+          <t>-0,88; 3,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 2,72</t>
+          <t>-1,49; 2,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 8,9</t>
+          <t>4,42; 8,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,24; 4,19</t>
+          <t>0,3; 4,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 2,46</t>
+          <t>-0,7; 2,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,1; 7,6</t>
+          <t>4,15; 7,54</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 223,04</t>
+          <t>-8,13; 226,89</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-30,31; 146,77</t>
+          <t>-25,07; 141,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48,01; 300,2</t>
+          <t>54,91; 326,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-29,71; 248,42</t>
+          <t>-33,4; 269,29</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,61; 189,85</t>
+          <t>-49,23; 216,63</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>107,16; 635,86</t>
+          <t>109,88; 640,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,66; 174,76</t>
+          <t>4,43; 180,15</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-22,16; 102,15</t>
+          <t>-19,5; 110,9</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>96,42; 315,63</t>
+          <t>102,44; 334,4</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,06; 5,85</t>
+          <t>3,01; 5,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,88</t>
+          <t>2,27; 5,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3,11; 7,18</t>
+          <t>2,66; 7,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,81</t>
+          <t>2,99; 5,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 4,59</t>
+          <t>1,74; 4,75</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,27; 24,47</t>
+          <t>5,31; 26,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,44; 5,4</t>
+          <t>3,5; 5,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,25</t>
+          <t>2,36; 4,22</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 17,2</t>
+          <t>5,4; 18,67</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>48,37; 112,18</t>
+          <t>46,87; 109,86</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34,73; 91,32</t>
+          <t>35,75; 97,13</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55,02; 135,82</t>
+          <t>47,65; 133,07</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,97; 80,06</t>
+          <t>33,3; 80,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>19,13; 62,59</t>
+          <t>20,15; 65,4</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,77; 338,28</t>
+          <t>64,9; 351,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>46,76; 84,1</t>
+          <t>48,09; 85,54</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,58; 66,95</t>
+          <t>31,72; 65,94</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77,17; 246,22</t>
+          <t>77,11; 275,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P16A15-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P16A15-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12,52</t>
+          <t>10,83</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,13</t>
+          <t>15,15</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>14,21</t>
+          <t>13,47</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,25; 12,87</t>
+          <t>6,28; 13,04</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,94; 12,92</t>
+          <t>5,9; 12,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,79; 16,41</t>
+          <t>7,15; 14,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,86; 12,02</t>
+          <t>6,16; 12,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>5,78; 12,67</t>
+          <t>5,37; 12,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,02; 18,24</t>
+          <t>12,03; 18,37</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,17; 11,67</t>
+          <t>7,11; 11,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,93; 11,81</t>
+          <t>6,79; 11,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,82; 16,78</t>
+          <t>11,23; 15,89</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>110,72%</t>
+          <t>95,77%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>98,15%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>104,41%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>49,8; 131,31</t>
+          <t>46,56; 129,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>46,21; 128,7</t>
+          <t>46,42; 131,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,18; 164,74</t>
+          <t>57,1; 147,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33,85; 85,55</t>
+          <t>36,44; 86,63</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>34,49; 90,53</t>
+          <t>32,33; 89,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,64; 130,81</t>
+          <t>70,57; 133,03</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,29; 91,77</t>
+          <t>47,8; 92,35</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,58; 92,08</t>
+          <t>47,54; 93,3</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>80,42; 132,92</t>
+          <t>76,65; 125,62</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6,21</t>
+          <t>7,17</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>14,07</t>
+          <t>5,9</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10,09</t>
+          <t>6,54</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,23; 4,01</t>
+          <t>1,44; 4,16</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,85; 4,65</t>
+          <t>1,97; 4,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,37; 7,95</t>
+          <t>5,87; 8,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,43; 3,48</t>
+          <t>0,48; 3,39</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,61</t>
+          <t>1,69; 4,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,29; 37,28</t>
+          <t>4,55; 7,31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,45; 3,49</t>
+          <t>1,38; 3,43</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,22</t>
+          <t>2,17; 4,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5,53; 22,6</t>
+          <t>5,52; 7,46</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>195,4%</t>
+          <t>225,64%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>425,07%</t>
+          <t>178,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>311,38%</t>
+          <t>201,88%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>30,26; 153,92</t>
+          <t>37,78; 156,13</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>45,67; 173,26</t>
+          <t>52,46; 176,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88,47; 296,89</t>
+          <t>150,79; 336,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,67; 128,07</t>
+          <t>11,58; 129,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>41,98; 175,56</t>
+          <t>38,2; 166,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>151,12; 1314,3</t>
+          <t>112,27; 288,32</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>38,07; 120,8</t>
+          <t>37,33; 126,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>58,12; 148,78</t>
+          <t>55,97; 151,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>167,41; 747,18</t>
+          <t>144,17; 267,16</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,28</t>
+          <t>5,36</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,66</t>
+          <t>6,82</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5,93</t>
+          <t>6,05</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 6,39</t>
+          <t>0,26; 6,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,83</t>
+          <t>-1,47; 3,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,86; 8,05</t>
+          <t>2,89; 7,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,88; 3,9</t>
+          <t>-1,05; 3,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,49; 2,92</t>
+          <t>-1,61; 3,02</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,42; 8,95</t>
+          <t>4,45; 8,8</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 4,31</t>
+          <t>0,16; 4,08</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,58</t>
+          <t>-0,69; 2,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>4,15; 7,54</t>
+          <t>4,4; 7,97</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>144,46%</t>
+          <t>146,61%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>277,02%</t>
+          <t>283,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>192,69%</t>
+          <t>196,53%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,13; 226,89</t>
+          <t>3,82; 237,76</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-25,07; 141,33</t>
+          <t>-32,27; 139,44</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>54,91; 326,29</t>
+          <t>54,48; 310,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,4; 269,29</t>
+          <t>-34,82; 270,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-49,23; 216,63</t>
+          <t>-50,58; 198,85</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>109,88; 640,47</t>
+          <t>110,81; 625,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4,43; 180,15</t>
+          <t>2,1; 167,47</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-19,5; 110,9</t>
+          <t>-19,11; 116,4</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>102,44; 334,4</t>
+          <t>108,75; 350,09</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5,63</t>
+          <t>6,19</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,69</t>
+          <t>6,02</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>8,25</t>
+          <t>6,12</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>3,01; 5,78</t>
+          <t>3,15; 5,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 5,03</t>
+          <t>2,33; 4,86</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,66; 7,08</t>
+          <t>4,92; 7,52</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,99; 5,93</t>
+          <t>2,93; 5,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,75</t>
+          <t>1,78; 4,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,31; 26,01</t>
+          <t>4,76; 7,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,5; 5,52</t>
+          <t>3,48; 5,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 4,22</t>
+          <t>2,33; 4,29</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>5,4; 18,67</t>
+          <t>5,14; 7,06</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>106,43%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>135,46%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>120,0%</t>
+          <t>88,99%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>46,87; 109,86</t>
+          <t>49,47; 113,3</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>35,75; 97,13</t>
+          <t>35,29; 90,94</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>47,65; 133,07</t>
+          <t>76,27; 143,18</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33,3; 80,85</t>
+          <t>34,9; 81,06</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20,15; 65,4</t>
+          <t>20,24; 65,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>64,9; 351,63</t>
+          <t>55,6; 105,0</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>48,09; 85,54</t>
+          <t>47,47; 82,82</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>31,72; 65,94</t>
+          <t>32,13; 68,03</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>77,11; 275,91</t>
+          <t>70,27; 112,22</t>
         </is>
       </c>
     </row>
